--- a/02_加值成品/八上/八上1-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上1-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上1-3 質量的測量　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二上學期 八上1-3 質量的測量　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>質量的SI單位是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>歸零鍵</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>鑷子</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>公斤(kg)</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>基本量</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>1公斤等於幾公克？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>3000 g</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>0.5 kg</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>2500 g</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>1000 g</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>×1000</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>測質量常用的工具？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>質量</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>質量相等</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>天平</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>鑷子</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>平衡原理</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>物質所含物質的多寡稱為？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>質量</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>公克g</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>重力</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>鑷子</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>非重量</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>重量是物體受到的什麼？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>天平</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>歸零(校正)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>重量(力)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>重力</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>單位N</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>1公克等於幾毫克？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>避免手上油污增加質量</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>墊稱量紙或容器</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>不能直接，彈簧秤測重量</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>1000 mg</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>×1000</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>使用天平前要先做什麼？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>砝碼太重</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>重量(力)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>重力</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>歸零(校正)</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>確保準確</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>夾取砝碼應用什麼？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>天平</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>公克g</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>鑷子</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>公斤(kg)</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>避免油污</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>質量常用的較小單位是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>會</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>砝碼太重</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>重力</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>公克g</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>單位</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>天平兩端平衡表示兩側？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>質量相等</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>歸零(校正)</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>公克g</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>重量(力)</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>平衡</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上1-3 質量的測量　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二上學期 八上1-3 質量的測量　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>太空人到月球，質量如何變化？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>不變</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>公克g</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>重力</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>偏大</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>質量與位置無關</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>太空人到月球，重量如何變化？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>變小</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>鑷子</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>歸零(校正)</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>月球重力較小</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>500g 等於幾公斤？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>0.5 kg</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>2500 g</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>3000 g</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1000 g</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>÷1000</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>牛頓(N)是哪個量的單位？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>偏大</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>重力</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>砝碼太重</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>重量(力)</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>非質量</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>稱化學藥品應如何？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>1500 kg</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>墊稱量紙或容器</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>1000 mg</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>250000 mg</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>保護天平</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>2.5 kg 等於幾公克？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>3000 g</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>0.5 kg</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>1000 g</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>2500 g</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>×1000</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>天平未歸零偏正，讀數偏？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>天平</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>質量相等</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>會</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>偏大</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>系統誤差</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>電子天平使用前按什麼鍵？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>變小</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>會</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>歸零鍵</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>質量</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>扣除容器</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>3 kg 等於幾公克？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>1000 g</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>3000 g</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>0.5 kg</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>2500 g</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>×1000</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>物體的重量會隨所在星球改變嗎？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>會</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>公斤(kg)</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>砝碼太重</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>質量</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>受重力</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上1-3 質量的測量　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二上學期 八上1-3 質量的測量　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>同一物體在地球與月球，何者不變？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>質量</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>鑷子</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>重力</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>偏大</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>重量會變</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何用鑷子而非手取砝碼？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>避免手上油污增加質量</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>扣除(歸零或相減)</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>墊稱量紙或容器</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>能，質量與重力無關</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>精密考量</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>質量能用彈簧秤直接測嗎？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>避免手上油污增加質量</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>能，質量與重力無關</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>1000 mg</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>不能直接，彈簧秤測重量</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>需換算</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>先放物再放砝碼，天平右偏表示？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>砝碼太重</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>歸零(校正)</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>公斤(kg)</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>需減砝碼</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>1公噸等於幾公斤？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>不能直接，彈簧秤測重量</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>墊稱量紙或容器</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>1000 kg</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1000 mg</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>大單位</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>稱量前容器質量要如何處理？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>1000 kg</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>1000 mg</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>避免手上油污增加質量</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>扣除(歸零或相減)</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>得淨質量</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>無重力太空中能測質量嗎？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>能，質量與重力無關</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>天平測質量不受重力、彈簧秤測重量會</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>扣除(歸零或相減)</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>墊稱量紙或容器</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>用慣性法</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>0.25 kg 等於幾 mg？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>避免手上油污增加質量</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>扣除(歸零或相減)</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>1000 mg</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>250000 mg</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>kg→g→mg</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>天平測質量與彈簧秤測重量的差別？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>扣除(歸零或相減)</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>能，質量與重力無關</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>天平測質量不受重力、彈簧秤測重量會</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>避免手上油污增加質量</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>區別</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>1.5 公噸等於幾公斤？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>1000 kg</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>墊稱量紙或容器</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>避免手上油污增加質量</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>1500 kg</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>×1000</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八上/八上1-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上1-3_三種難度測驗卷.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>物質所含物質的多寡稱為？</t>
+          <t>物體所含物質的多寡稱為？</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -688,17 +688,17 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>公克g</t>
+          <t>變小</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>重力</t>
+          <t>鑷子</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>鑷子</t>
+          <t>公斤(kg)</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>天平未歸零偏正，讀數偏？</t>
+          <t>天平未歸零、指針原本就偏向重的一側，之後量得的讀數會？</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>質量相等</t>
+          <t>鑷子</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>會</t>
+          <t>公克g</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">

--- a/02_加值成品/八上/八上1-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上1-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>基本量</t>
+          <t>基本量：國際單位制規定質量的基本單位是公斤，符號寫作kg</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>×1000</t>
+          <t>×1000：1公斤等於1000公克，公斤換算公克要乘以1000</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>平衡原理</t>
+          <t>平衡原理：天平利用兩邊平衡來比較物體和砝碼的質量，是常用的測質量工具</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>非重量</t>
+          <t>非重量：質量是指物體本身所含物質的多寡，不會因為所在位置改變而改變，這和會隨重力改變的重量不同</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>單位N</t>
+          <t>單位N：重量是物體受到地球(或其他星球)重力吸引的力，單位是牛頓(N)</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>×1000</t>
+          <t>×1000：1公克等於1000毫克，公克換算毫克要乘以1000</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>確保準確</t>
+          <t>確保準確：使用天平前要先歸零校正，確認指針指向正確的平衡位置，才能量出準確的質量</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>避免油污</t>
+          <t>避免油污：用鑷子夾取砝碼可以避免手上的油污和汗水沾到砝碼，影響砝碼原本的質量</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>單位</t>
+          <t>單位：測量較輕的物體時常用比公斤小的公克(g)作單位</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>平衡</t>
+          <t>平衡：天平兩端達到平衡狀態時，代表兩邊承受的質量相等</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>質量與位置無關</t>
+          <t>質量與位置無關：質量是物體本身所含物質的多寡，不會因為所在位置或重力大小不同而改變，所以到月球質量仍然不變</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>月球重力較小</t>
+          <t>月球重力較小：月球的重力只有地球的約六分之一，重量是重力造成的，重力變小重量也會跟著變小</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>÷1000</t>
+          <t>÷1000：1公斤等於1000公克，500除以1000等於0.5公斤</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>非質量</t>
+          <t>非質量：牛頓是力的單位，重量本質上是一種力，所以用牛頓當單位；質量的單位則是公斤，兩者不同</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>保護天平</t>
+          <t>保護天平：秤化學藥品時要先墊稱量紙或使用容器，避免藥品直接接觸並腐蝕或弄髒天平的秤盤</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>×1000</t>
+          <t>×1000：1公斤等於1000公克，2.5乘以1000等於2500公克</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>系統誤差</t>
+          <t>系統誤差：天平沒有歸零，指針一開始就偏向重的一側，之後測量任何物體時讀數都會固定多出一些，這種每次都偏同一方向的誤差稱為系統誤差</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>扣除容器</t>
+          <t>扣除容器：使用電子天平前先按歸零鍵，可以把容器本身的質量扣除，之後顯示的就是待測物真正的淨質量</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>×1000</t>
+          <t>×1000：1公斤等於1000公克，3公斤乘以1000等於3000公克</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>受重力</t>
+          <t>受重力：重量是物體受到的重力大小，不同星球的重力不同，所以同一物體的重量會隨所在星球改變，但質量不變</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>重量會變</t>
+          <t>重量會變：質量是物體本身所含物質多寡，不受所在位置影響，所以同一物體在地球和月球的質量相同，但重量會因重力不同而改變</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>精密考量</t>
+          <t>精密考量：手上的油脂和汗水沾到砝碼上會增加砝碼的質量，影響測量的精密度，所以要用鑷子夾取</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>需換算</t>
+          <t>需換算：彈簧秤是靠重力拉伸彈簧來測量重量(力)，不是直接測質量，若要得到質量需要用測得的重量除以重力加速度換算</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>需減砝碼</t>
+          <t>需減砝碼：天平向放砝碼的那一側(右邊)偏，代表右邊砝碼的總質量比左邊物體重，所以要減少砝碼才能達到平衡</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>大單位</t>
+          <t>大單位：公噸是比公斤更大的質量單位，1公噸等於1000公斤，常用來表示很重的物體</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>得淨質量</t>
+          <t>得淨質量：稱量藥品前要先扣除容器本身的質量(可用歸零功能，或先秤空容器再相減)，這樣才能得到藥品真正的淨質量</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>用慣性法</t>
+          <t>用慣性法：質量是物體慣性大小的量度，跟重力無關，即使在無重力的太空中，也能利用物體對抗外力改變運動狀態的慣性大小來測量質量</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>kg→g→mg</t>
+          <t>kg→g→mg：先把0.25公斤乘以1000換算成250公克，再把250公克乘以1000換算成250000毫克</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>區別</t>
+          <t>區別：天平是靠比較砝碼與物體的質量來平衡，不受當地重力大小影響；彈簧秤則是靠重力拉伸彈簧來測量重量，會隨重力大小改變讀數</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>×1000</t>
+          <t>×1000：1公噸等於1000公斤，1.5乘以1000等於1500公斤</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八上/八上1-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上1-3_三種難度測驗卷.xlsx
@@ -688,17 +688,17 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>變小</t>
+          <t>重力</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>鑷子</t>
+          <t>歸零鍵</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>公斤(kg)</t>
+          <t>天平</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>歸零(校正)</t>
+          <t>變小</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>公克g</t>
+          <t>砝碼太重</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>重量(力)</t>
+          <t>鑷子</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>鑷子</t>
+          <t>天平</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>重力</t>
+          <t>公斤(kg)</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>偏大</t>
+          <t>會</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
